--- a/data/trending_integrated_20260914_15.xlsx
+++ b/data/trending_integrated_20260914_15.xlsx
@@ -578,13 +578,13 @@
         <v>-0.28</v>
       </c>
       <c r="E2" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F2" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G2" t="n">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="H2" t="n">
         <v>17.67</v>
@@ -610,7 +610,7 @@
         <v>17.95</v>
       </c>
       <c r="O2" t="n">
-        <v>270996971275</v>
+        <v>271159966445</v>
       </c>
       <c r="P2" t="n">
         <v>22450</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>차세대 광반도체 및 광통신 테마 상승 기대감. 단기 시세 과열 및 급락 조심 경고.</t>
+          <t>차세대 광반도체 및 광통신 관련주로 급등 가능성에 대한 기대감 형성. 단기 시세 끝 조심 의견도 존재.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광반도체', '광통신', '테마주']</t>
+          <t>['광통신', '광반도체', '주포']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6970</v>
+        <v>6980</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+26.50%</t>
+          <t>+26.68%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F3" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G3" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H3" t="n">
         <v>1.67</v>
@@ -702,7 +702,7 @@
         <v>1.68</v>
       </c>
       <c r="O3" t="n">
-        <v>73242620290</v>
+        <v>75090297080</v>
       </c>
       <c r="P3" t="n">
         <v>10360</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9050</v>
+        <v>9040</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+14.41%</t>
+          <t>+14.29%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.55</v>
       </c>
       <c r="E4" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F4" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G4" t="n">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="H4" t="n">
         <v>1.25</v>
@@ -794,7 +794,7 @@
         <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>119973326125</v>
+        <v>122356539675</v>
       </c>
       <c r="P4" t="n">
         <v>25050</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2915</v>
+        <v>2940</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+12.77%</t>
+          <t>+13.73%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -860,7 +860,7 @@
         <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H5" t="n">
         <v>3.6</v>
@@ -886,7 +886,7 @@
         <v>3.64</v>
       </c>
       <c r="O5" t="n">
-        <v>39579675492</v>
+        <v>39883997752</v>
       </c>
       <c r="P5" t="n">
         <v>6180</v>
@@ -935,21 +935,21 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4310</v>
+        <v>4325</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+11.37%</t>
+          <t>+11.76%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.45</v>
       </c>
       <c r="E6" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F6" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G6" t="n">
         <v>324</v>
@@ -978,7 +978,7 @@
         <v>1.04</v>
       </c>
       <c r="O6" t="n">
-        <v>304902210546</v>
+        <v>307734191517</v>
       </c>
       <c r="P6" t="n">
         <v>8100</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9020</v>
+        <v>9130</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+8.81%</t>
+          <t>+10.13%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G7" t="n">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="H7" t="n">
         <v>0.83</v>
@@ -1070,7 +1070,7 @@
         <v>0.82</v>
       </c>
       <c r="O7" t="n">
-        <v>46036009095</v>
+        <v>47029096705</v>
       </c>
       <c r="P7" t="n">
         <v>12800</v>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2810</v>
+        <v>2790</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+7.25%</t>
+          <t>+6.49%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1136,7 +1136,7 @@
         <v>49</v>
       </c>
       <c r="G8" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H8" t="n">
         <v>1.44</v>
@@ -1162,7 +1162,7 @@
         <v>3.83</v>
       </c>
       <c r="O8" t="n">
-        <v>104478349488</v>
+        <v>105033400957</v>
       </c>
       <c r="P8" t="n">
         <v>4810</v>
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8820</v>
+        <v>17000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+6.39%</t>
+          <t>+5.85%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.54</v>
+        <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>317</v>
+        <v>145</v>
       </c>
       <c r="F9" t="n">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="G9" t="n">
-        <v>1903</v>
+        <v>248</v>
       </c>
       <c r="H9" t="n">
-        <v>0.75</v>
+        <v>2.7</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>8290</v>
+        <v>16060</v>
       </c>
       <c r="K9" t="n">
-        <v>8100</v>
+        <v>16780</v>
       </c>
       <c r="L9" t="n">
-        <v>9240</v>
+        <v>18610</v>
       </c>
       <c r="M9" t="n">
-        <v>8060</v>
+        <v>16230</v>
       </c>
       <c r="N9" t="n">
-        <v>1.29</v>
+        <v>2.39</v>
       </c>
       <c r="O9" t="n">
-        <v>46052840965</v>
+        <v>278325611225</v>
       </c>
       <c r="P9" t="n">
-        <v>21500</v>
+        <v>30550</v>
       </c>
       <c r="Q9" t="n">
-        <v>2300</v>
+        <v>6100</v>
       </c>
       <c r="R9" t="n">
-        <v>-27000</v>
+        <v>-295000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>신약 개발 관련 심포지엄 및 임상 결과 발표 임박. 글로벌 제약사 협력 및 기대감.</t>
+          <t>AI 개발 속도 조절론이 악재로 작용하며 주가 하락. 프로그램 매도세와 고가 대비 하락폭에 대한 불만 제기.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['신약개발', '임상결과', '바이오']</t>
+          <t>['AI', '보안주', '개미']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17020</v>
+        <v>22100</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+5.98%</t>
+          <t>+3.27%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.31</v>
+        <v>-0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F10" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G10" t="n">
-        <v>234</v>
+        <v>504</v>
       </c>
       <c r="H10" t="n">
-        <v>2.7</v>
+        <v>28.81</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>16060</v>
+        <v>21400</v>
       </c>
       <c r="K10" t="n">
-        <v>16780</v>
+        <v>21100</v>
       </c>
       <c r="L10" t="n">
-        <v>18610</v>
+        <v>22500</v>
       </c>
       <c r="M10" t="n">
-        <v>16230</v>
+        <v>20850</v>
       </c>
       <c r="N10" t="n">
-        <v>2.39</v>
+        <v>28.89</v>
       </c>
       <c r="O10" t="n">
-        <v>276933877625</v>
+        <v>92193821825</v>
       </c>
       <c r="P10" t="n">
-        <v>30550</v>
+        <v>35350</v>
       </c>
       <c r="Q10" t="n">
-        <v>6100</v>
+        <v>18440</v>
       </c>
       <c r="R10" t="n">
-        <v>-295000</v>
+        <v>688000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>49000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>AI 개발 속도 조절론 관련 논란. 보안주로서의 가능성과 단기 급락에 대한 언급.</t>
+          <t>대형 상선 6척 수주 소식 및 증권사 목표가 상향. 조선업 호황 속 숏커버 및 실적 개선 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['AI', '보안주', '급락']</t>
+          <t>['수주', '조선업', '숏커버']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22100</v>
+        <v>14500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+3.27%</t>
+          <t>+2.47%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.08</v>
+        <v>-0.62</v>
       </c>
       <c r="E11" t="n">
-        <v>140</v>
+        <v>230</v>
       </c>
       <c r="F11" t="n">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="G11" t="n">
-        <v>504</v>
+        <v>879</v>
       </c>
       <c r="H11" t="n">
-        <v>28.81</v>
+        <v>1.88</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>21400</v>
+        <v>14150</v>
       </c>
       <c r="K11" t="n">
-        <v>21100</v>
+        <v>13850</v>
       </c>
       <c r="L11" t="n">
-        <v>22500</v>
+        <v>14950</v>
       </c>
       <c r="M11" t="n">
-        <v>20850</v>
+        <v>13800</v>
       </c>
       <c r="N11" t="n">
-        <v>28.89</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
-        <v>89734232850</v>
+        <v>176112988950</v>
       </c>
       <c r="P11" t="n">
-        <v>35350</v>
+        <v>31500</v>
       </c>
       <c r="Q11" t="n">
-        <v>18440</v>
+        <v>1272</v>
       </c>
       <c r="R11" t="n">
-        <v>688000</v>
+        <v>-325000</v>
       </c>
       <c r="S11" t="n">
-        <v>49000</v>
+        <v>-3000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>대형 수주 공시 확인 및 숏커버, 목표주가 상향 등 긍정적 뉴스 기반 분석.</t>
+          <t>AIDC 광통신 기술 발전 뉴스와 함께 향후 주가 상승에 대한 기대감 표출.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['수주', '숏커버', '목표주가']</t>
+          <t>['광통신', 'AIDC', '기술력']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14440</v>
+        <v>8490</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+2.05%</t>
+          <t>+2.41%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.62</v>
+        <v>-0.54</v>
       </c>
       <c r="E12" t="n">
-        <v>227</v>
+        <v>350</v>
       </c>
       <c r="F12" t="n">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="G12" t="n">
-        <v>874</v>
+        <v>2082</v>
       </c>
       <c r="H12" t="n">
-        <v>1.88</v>
+        <v>0.75</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14150</v>
+        <v>8290</v>
       </c>
       <c r="K12" t="n">
-        <v>13850</v>
+        <v>8100</v>
       </c>
       <c r="L12" t="n">
-        <v>14950</v>
+        <v>9240</v>
       </c>
       <c r="M12" t="n">
-        <v>13800</v>
+        <v>8060</v>
       </c>
       <c r="N12" t="n">
-        <v>2.5</v>
+        <v>1.29</v>
       </c>
       <c r="O12" t="n">
-        <v>174075211185</v>
+        <v>48897674345</v>
       </c>
       <c r="P12" t="n">
-        <v>31500</v>
+        <v>21500</v>
       </c>
       <c r="Q12" t="n">
-        <v>1272</v>
+        <v>2300</v>
       </c>
       <c r="R12" t="n">
-        <v>-325000</v>
+        <v>-27000</v>
       </c>
       <c r="S12" t="n">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>AIDC 광통신 기술 발전 뉴스와 함께 향후 주가 상승에 대한 기대감 표출.</t>
+          <t>신약 개발 관련 심포지엄 및 임상 결과 발표 임박. 글로벌 제약사 협력 및 기대감.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['광통신', 'AIDC', '기술력']</t>
+          <t>['신약개발', '임상결과', '바이오']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14820</v>
+        <v>14670</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+0.41%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-1.97</v>
       </c>
       <c r="E13" t="n">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F13" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G13" t="n">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="H13" t="n">
         <v>1.17</v>
@@ -1622,7 +1622,7 @@
         <v>3.14</v>
       </c>
       <c r="O13" t="n">
-        <v>123818398490</v>
+        <v>125226578300</v>
       </c>
       <c r="P13" t="n">
         <v>36200</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1840</v>
+        <v>1836</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.02%</t>
+          <t>-2.24%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.36</v>
       </c>
       <c r="E14" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F14" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G14" t="n">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="H14" t="n">
         <v>2.08</v>
@@ -1708,13 +1708,13 @@
         <v>1961</v>
       </c>
       <c r="M14" t="n">
-        <v>1837</v>
+        <v>1835</v>
       </c>
       <c r="N14" t="n">
         <v>2.44</v>
       </c>
       <c r="O14" t="n">
-        <v>17353885995</v>
+        <v>17591284381</v>
       </c>
       <c r="P14" t="n">
         <v>4795</v>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>249000</v>
+        <v>249500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-4.05%</t>
+          <t>-3.85%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="G15" t="n">
-        <v>1681</v>
+        <v>1717</v>
       </c>
       <c r="H15" t="n">
         <v>46.64</v>
@@ -1806,7 +1806,7 @@
         <v>46.71</v>
       </c>
       <c r="O15" t="n">
-        <v>3686047066750</v>
+        <v>3755386190250</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>AI 속도 조절론 관련 언급. 정치적 이슈와 함께 주가 부진에 대한 불만 표출.</t>
+          <t>AI 속도 조절론, 정치적 이슈와 연관된 부정적 언급 다수. 호재에 반응 없고 악재에 민감하다는 지적.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['AI', '반도체', '주가부진']</t>
+          <t>['AI', '이재명', '주주']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>86800</v>
+        <v>86900</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-4.41%</t>
+          <t>-4.30%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.03</v>
       </c>
       <c r="E16" t="n">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="F16" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G16" t="n">
-        <v>906</v>
+        <v>933</v>
       </c>
       <c r="H16" t="n">
         <v>23.56</v>
@@ -1898,7 +1898,7 @@
         <v>23.59</v>
       </c>
       <c r="O16" t="n">
-        <v>228582182650</v>
+        <v>238440993600</v>
       </c>
       <c r="P16" t="n">
         <v>139200</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>국제 유가 상승 및 원전 관련 긍정적 전망. 금리 인상 분위기 및 프로그램 매도에 대한 우려.</t>
+          <t>국제 유가 상승에 따른 원전주 상승 가능성 언급. 차트 분석과 함께 오후 반등 기대감 형성.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['원전', '국제유가', '금리']</t>
+          <t>['원전', '유가', '차트']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1943,184 +1943,184 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>11570</v>
+        <v>18710</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-5.86%</t>
+          <t>-5.93%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.72</v>
+        <v>-0.1</v>
       </c>
       <c r="E17" t="n">
-        <v>83</v>
+        <v>127</v>
       </c>
       <c r="F17" t="n">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="G17" t="n">
-        <v>126</v>
+        <v>524</v>
       </c>
       <c r="H17" t="n">
-        <v>0.22</v>
+        <v>10.55</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>12290</v>
+        <v>19890</v>
       </c>
       <c r="K17" t="n">
-        <v>12030</v>
+        <v>19480</v>
       </c>
       <c r="L17" t="n">
-        <v>13230</v>
+        <v>19550</v>
       </c>
       <c r="M17" t="n">
-        <v>11470</v>
+        <v>18500</v>
       </c>
       <c r="N17" t="n">
-        <v>0.9399999999999999</v>
+        <v>10.65</v>
       </c>
       <c r="O17" t="n">
-        <v>60083526550</v>
+        <v>81180366835</v>
       </c>
       <c r="P17" t="n">
-        <v>20850</v>
+        <v>40350</v>
       </c>
       <c r="Q17" t="n">
-        <v>4020</v>
+        <v>3320</v>
       </c>
       <c r="R17" t="n">
-        <v>22000</v>
+        <v>-531000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-246000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>원전주 전반의 하락세 및 재료 소멸 가능성 언급, 보유 물량 관리 및 신규 진입에 대한 보수적 관점.</t>
+          <t>대차해지 운동을 통한 공매도 세력 견제 및 주가 부양 의지를 보이는 게시글 다수.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['원전주', '폭락', '재료 소멸']</t>
+          <t>['대차해지', '공매도', '주가']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18680</v>
+        <v>11520</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-6.08%</t>
+          <t>-6.27%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.1</v>
+        <v>-0.72</v>
       </c>
       <c r="E18" t="n">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="F18" t="n">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="G18" t="n">
-        <v>514</v>
+        <v>126</v>
       </c>
       <c r="H18" t="n">
-        <v>10.55</v>
+        <v>0.22</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>19890</v>
+        <v>12290</v>
       </c>
       <c r="K18" t="n">
-        <v>19480</v>
+        <v>12030</v>
       </c>
       <c r="L18" t="n">
-        <v>19550</v>
+        <v>13230</v>
       </c>
       <c r="M18" t="n">
-        <v>18500</v>
+        <v>11470</v>
       </c>
       <c r="N18" t="n">
-        <v>10.65</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>79904156570</v>
+        <v>60369789735</v>
       </c>
       <c r="P18" t="n">
-        <v>40350</v>
+        <v>20850</v>
       </c>
       <c r="Q18" t="n">
-        <v>3320</v>
+        <v>4020</v>
       </c>
       <c r="R18" t="n">
-        <v>-531000</v>
+        <v>22000</v>
       </c>
       <c r="S18" t="n">
-        <v>-246000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>대차해지 운동을 통한 공매도 세력 견제 및 주가 부양 의지를 보이는 게시글 다수.</t>
+          <t>원전주 전반의 하락세 및 재료 소멸 가능성 언급, 보유 물량 관리 및 신규 진입에 대한 보수적 관점.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['대차해지', '공매도', '주가']</t>
+          <t>['원전주', '폭락', '재료 소멸']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1693000</v>
+        <v>1691000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-6.57%</t>
+          <t>-6.68%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>492</v>
+        <v>506</v>
       </c>
       <c r="G19" t="n">
-        <v>1759</v>
+        <v>1735</v>
       </c>
       <c r="H19" t="n">
         <v>50.47</v>
@@ -2168,13 +2168,13 @@
         <v>1740000</v>
       </c>
       <c r="M19" t="n">
-        <v>1692000</v>
+        <v>1690000</v>
       </c>
       <c r="N19" t="n">
         <v>50.55</v>
       </c>
       <c r="O19" t="n">
-        <v>5582528941000</v>
+        <v>5812390238500</v>
       </c>
       <c r="P19" t="n">
         <v>2987000</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>AI 개발 속도 조절론 및 국내 정치 상황 언급. 반도체 섹터 전반의 하락 추세 및 불안감.</t>
+          <t>정치적 상황 및 정부 정책에 대한 부정적 언급이 주를 이루며, 주가 하락에 대한 우려 표출.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['AI', '반도체', '주가하락']</t>
+          <t>['정부', '반도체', '하락']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13640</v>
+        <v>13580</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-7.27%</t>
+          <t>-7.68%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F20" t="n">
         <v>62</v>
       </c>
       <c r="G20" t="n">
-        <v>449</v>
+        <v>471</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2260,13 +2260,13 @@
         <v>15420</v>
       </c>
       <c r="M20" t="n">
-        <v>13590</v>
+        <v>13580</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>32465121895</v>
+        <v>33010478130</v>
       </c>
       <c r="P20" t="n">
         <v>19380</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11090</v>
+        <v>11060</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-10.92%</t>
+          <t>-11.16%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.51</v>
       </c>
       <c r="E21" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F21" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G21" t="n">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="H21" t="n">
         <v>17.58</v>
@@ -2358,7 +2358,7 @@
         <v>17.07</v>
       </c>
       <c r="O21" t="n">
-        <v>68576847450</v>
+        <v>69153045630</v>
       </c>
       <c r="P21" t="n">
         <v>14350</v>

--- a/data/trending_integrated_20260914_15.xlsx
+++ b/data/trending_integrated_20260914_15.xlsx
@@ -584,7 +584,7 @@
         <v>114</v>
       </c>
       <c r="G2" t="n">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="H2" t="n">
         <v>17.67</v>
@@ -610,7 +610,7 @@
         <v>17.95</v>
       </c>
       <c r="O2" t="n">
-        <v>271159966445</v>
+        <v>271258034675</v>
       </c>
       <c r="P2" t="n">
         <v>22450</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>차세대 광반도체 및 광통신 관련주로 급등 가능성에 대한 기대감 형성. 단기 시세 끝 조심 의견도 존재.</t>
+          <t>차세대 광반도체 및 광통신 테마 기대감 속 3연상 및 텐버거 전망. 시세 끝 및 급락 조심론도 공존.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광통신', '광반도체', '주포']</t>
+          <t>['광반도체', '광통신', '텐버거']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6980</v>
+        <v>6850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+26.68%</t>
+          <t>+24.32%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F3" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G3" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="H3" t="n">
         <v>1.67</v>
@@ -702,7 +702,7 @@
         <v>1.68</v>
       </c>
       <c r="O3" t="n">
-        <v>75090297080</v>
+        <v>78121775125</v>
       </c>
       <c r="P3" t="n">
         <v>10360</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9040</v>
+        <v>9190</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+14.29%</t>
+          <t>+16.18%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.55</v>
       </c>
       <c r="E4" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F4" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G4" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H4" t="n">
         <v>1.25</v>
@@ -794,7 +794,7 @@
         <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>122356539675</v>
+        <v>124075390505</v>
       </c>
       <c r="P4" t="n">
         <v>25050</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2940</v>
+        <v>2925</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+13.73%</t>
+          <t>+13.15%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.04</v>
       </c>
       <c r="E5" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F5" t="n">
         <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="H5" t="n">
         <v>3.6</v>
@@ -886,7 +886,7 @@
         <v>3.64</v>
       </c>
       <c r="O5" t="n">
-        <v>39883997752</v>
+        <v>40188474729</v>
       </c>
       <c r="P5" t="n">
         <v>6180</v>
@@ -946,13 +946,13 @@
         <v>-0.45</v>
       </c>
       <c r="E6" t="n">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F6" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G6" t="n">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="H6" t="n">
         <v>0.59</v>
@@ -978,7 +978,7 @@
         <v>1.04</v>
       </c>
       <c r="O6" t="n">
-        <v>307734191517</v>
+        <v>312620497997</v>
       </c>
       <c r="P6" t="n">
         <v>8100</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>6G 시대 개막 및 국책사업 선정 가능성에 따른 기대감 표출.</t>
+          <t>6G 시대 개막 및 광전자, 빛샘전자 등 관련주 동반 상승 기대감. 국책사업 선정 시 8000원 이상 가치 주장.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['6G', '국책사업', '기대감']</t>
+          <t>['6G', '국책사업', '광전자']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9130</v>
+        <v>9210</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+10.13%</t>
+          <t>+11.10%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F7" t="n">
         <v>42</v>
       </c>
       <c r="G7" t="n">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="H7" t="n">
         <v>0.83</v>
@@ -1070,7 +1070,7 @@
         <v>0.82</v>
       </c>
       <c r="O7" t="n">
-        <v>47029096705</v>
+        <v>48632871925</v>
       </c>
       <c r="P7" t="n">
         <v>12800</v>
@@ -1119,18 +1119,18 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2790</v>
+        <v>2805</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+6.49%</t>
+          <t>+7.06%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-2.39</v>
       </c>
       <c r="E8" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F8" t="n">
         <v>49</v>
@@ -1162,7 +1162,7 @@
         <v>3.83</v>
       </c>
       <c r="O8" t="n">
-        <v>105033400957</v>
+        <v>105548938535</v>
       </c>
       <c r="P8" t="n">
         <v>4810</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17000</v>
+        <v>17080</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+5.85%</t>
+          <t>+6.35%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F9" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G9" t="n">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="H9" t="n">
         <v>2.7</v>
@@ -1254,7 +1254,7 @@
         <v>2.39</v>
       </c>
       <c r="O9" t="n">
-        <v>278325611225</v>
+        <v>280888385405</v>
       </c>
       <c r="P9" t="n">
         <v>30550</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>AI 개발 속도 조절론이 악재로 작용하며 주가 하락. 프로그램 매도세와 고가 대비 하락폭에 대한 불만 제기.</t>
+          <t>AI 개발 속도 조절론이 호재로 작용할 수 있다는 기대감과 프로그램 매도에 대한 우려 공존. 보안주로서의 가능성 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['AI', '보안주', '개미']</t>
+          <t>['AI', '보안주', '프로그램매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1314,13 +1314,13 @@
         <v>-0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F10" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G10" t="n">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="H10" t="n">
         <v>28.81</v>
@@ -1346,7 +1346,7 @@
         <v>28.89</v>
       </c>
       <c r="O10" t="n">
-        <v>92193821825</v>
+        <v>93501584925</v>
       </c>
       <c r="P10" t="n">
         <v>35350</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>대형 상선 6척 수주 소식 및 증권사 목표가 상향. 조선업 호황 속 숏커버 및 실적 개선 전망.</t>
+          <t>대형 상선 수주 (1.6조 원) 및 쇄빙선+LNG선+해상데이터센터 등 사업 전망. 증권사 목표가 상향 및 숏커버 기대감.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['수주', '조선업', '숏커버']</t>
+          <t>['수주', 'LNG선', '목표주가']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14500</v>
+        <v>14490</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+2.47%</t>
+          <t>+2.40%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.62</v>
       </c>
       <c r="E11" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="F11" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G11" t="n">
-        <v>879</v>
+        <v>902</v>
       </c>
       <c r="H11" t="n">
         <v>1.88</v>
@@ -1438,7 +1438,7 @@
         <v>2.5</v>
       </c>
       <c r="O11" t="n">
-        <v>176112988950</v>
+        <v>178371604515</v>
       </c>
       <c r="P11" t="n">
         <v>31500</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8490</v>
+        <v>8460</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+2.41%</t>
+          <t>+2.05%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.54</v>
       </c>
       <c r="E12" t="n">
-        <v>350</v>
+        <v>386</v>
       </c>
       <c r="F12" t="n">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="G12" t="n">
-        <v>2082</v>
+        <v>2247</v>
       </c>
       <c r="H12" t="n">
         <v>0.75</v>
@@ -1530,7 +1530,7 @@
         <v>1.29</v>
       </c>
       <c r="O12" t="n">
-        <v>48897674345</v>
+        <v>51237566340</v>
       </c>
       <c r="P12" t="n">
         <v>21500</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14670</v>
+        <v>14630</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-1.97</v>
       </c>
       <c r="E13" t="n">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="F13" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G13" t="n">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H13" t="n">
         <v>1.17</v>
@@ -1622,7 +1622,7 @@
         <v>3.14</v>
       </c>
       <c r="O13" t="n">
-        <v>125226578300</v>
+        <v>126670746400</v>
       </c>
       <c r="P13" t="n">
         <v>36200</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>중동 지정학적 리스크 및 국제 유가 급등에 따른 수혜 기대. 회담 연기 및 폭발음 관련 뉴스 주목.</t>
+          <t>이란-걸프 국가 회담 연기 및 호르무즈 해협 긴장 고조로 인한 유가 급등 기대감. 외인·기관 매도세 속 저가 매수 기회 논의.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['국제유가', '호르무즈', '지정학']</t>
+          <t>['국제유가', '호르무즈', '회담연기']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1682,13 +1682,13 @@
         <v>-0.36</v>
       </c>
       <c r="E14" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F14" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G14" t="n">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="H14" t="n">
         <v>2.08</v>
@@ -1708,13 +1708,13 @@
         <v>1961</v>
       </c>
       <c r="M14" t="n">
-        <v>1835</v>
+        <v>1831</v>
       </c>
       <c r="N14" t="n">
         <v>2.44</v>
       </c>
       <c r="O14" t="n">
-        <v>17591284381</v>
+        <v>17927680609</v>
       </c>
       <c r="P14" t="n">
         <v>4795</v>
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="G15" t="n">
-        <v>1717</v>
+        <v>1709</v>
       </c>
       <c r="H15" t="n">
         <v>46.64</v>
@@ -1806,7 +1806,7 @@
         <v>46.71</v>
       </c>
       <c r="O15" t="n">
-        <v>3755386190250</v>
+        <v>3850531393250</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>AI 속도 조절론, 정치적 이슈와 연관된 부정적 언급 다수. 호재에 반응 없고 악재에 민감하다는 지적.</t>
+          <t>AI 속도 조절론, 정치적 이슈, 미 선물 하락 등 복합적 악재 속 외국인·기관 매도세. 희망적인 전망은 찾아보기 어려움.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['AI', '이재명', '주주']</t>
+          <t>['AI', '외국인', '기관']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>86900</v>
+        <v>86700</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-4.30%</t>
+          <t>-4.52%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.03</v>
       </c>
       <c r="E16" t="n">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="F16" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="G16" t="n">
-        <v>933</v>
+        <v>955</v>
       </c>
       <c r="H16" t="n">
         <v>23.56</v>
@@ -1898,7 +1898,7 @@
         <v>23.59</v>
       </c>
       <c r="O16" t="n">
-        <v>238440993600</v>
+        <v>248342447750</v>
       </c>
       <c r="P16" t="n">
         <v>139200</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>국제 유가 상승에 따른 원전주 상승 가능성 언급. 차트 분석과 함께 오후 반등 기대감 형성.</t>
+          <t>정부 경제 정책에 대한 불만과 외국인·기관의 움직임에 대한 관망세. '희망 회로' 그만 굴리자는 자조적인 의견도 존재.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['원전', '유가', '차트']</t>
+          <t>['정부정책', '외국인', '기관']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18710</v>
+        <v>18760</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-5.93%</t>
+          <t>-5.68%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.1</v>
       </c>
       <c r="E17" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F17" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G17" t="n">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="H17" t="n">
         <v>10.55</v>
@@ -1990,7 +1990,7 @@
         <v>10.65</v>
       </c>
       <c r="O17" t="n">
-        <v>81180366835</v>
+        <v>82259294840</v>
       </c>
       <c r="P17" t="n">
         <v>40350</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>대차해지 운동을 통한 공매도 세력 견제 및 주가 부양 의지를 보이는 게시글 다수.</t>
+          <t>공매도 세력에 대한 반발과 '대차해지 운동' 동참 촉구. 주가 상승에 대한 기대보다는 공매도 세력과의 싸움에 집중하는 모습.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['대차해지', '공매도', '주가']</t>
+          <t>['대차해지', '공매도', '개미뭉치']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2050,13 +2050,13 @@
         <v>-0.72</v>
       </c>
       <c r="E18" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F18" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G18" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H18" t="n">
         <v>0.22</v>
@@ -2082,7 +2082,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>60369789735</v>
+        <v>60732469095</v>
       </c>
       <c r="P18" t="n">
         <v>20850</v>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1691000</v>
+        <v>1692000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-6.68%</t>
+          <t>-6.62%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2148,7 +2148,7 @@
         <v>506</v>
       </c>
       <c r="G19" t="n">
-        <v>1735</v>
+        <v>1677</v>
       </c>
       <c r="H19" t="n">
         <v>50.47</v>
@@ -2168,13 +2168,13 @@
         <v>1740000</v>
       </c>
       <c r="M19" t="n">
-        <v>1690000</v>
+        <v>1686000</v>
       </c>
       <c r="N19" t="n">
         <v>50.55</v>
       </c>
       <c r="O19" t="n">
-        <v>5812390238500</v>
+        <v>5980615719500</v>
       </c>
       <c r="P19" t="n">
         <v>2987000</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>정치적 상황 및 정부 정책에 대한 부정적 언급이 주를 이루며, 주가 하락에 대한 우려 표출.</t>
+          <t>정치적 불만과 '망할 정권' 언급이 주를 이루며, 반도체 시장 및 주가 하락에 대한 부정적 전망만 가득.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['정부', '반도체', '하락']</t>
+          <t>['반도체', '하락', '정치']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13580</v>
+        <v>13490</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-7.68%</t>
+          <t>-8.29%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="F20" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G20" t="n">
-        <v>471</v>
+        <v>486</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2260,13 +2260,13 @@
         <v>15420</v>
       </c>
       <c r="M20" t="n">
-        <v>13580</v>
+        <v>13330</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>33010478130</v>
+        <v>34286322880</v>
       </c>
       <c r="P20" t="n">
         <v>19380</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11060</v>
+        <v>10820</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-11.16%</t>
+          <t>-13.09%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.51</v>
       </c>
       <c r="E21" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F21" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G21" t="n">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="H21" t="n">
         <v>17.58</v>
@@ -2352,13 +2352,13 @@
         <v>13900</v>
       </c>
       <c r="M21" t="n">
-        <v>11050</v>
+        <v>10700</v>
       </c>
       <c r="N21" t="n">
         <v>17.07</v>
       </c>
       <c r="O21" t="n">
-        <v>69153045630</v>
+        <v>70897379240</v>
       </c>
       <c r="P21" t="n">
         <v>14350</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>주가 급락 및 투자 주의 공시에 대한 부정적 반응. 단기 급등락 반복에 대한 피로감.</t>
+          <t>투자주의 종목 지정 및 급락세 속 투자자들의 짜증과 불안감. 외인 대량 매수 언급도 있으나 전반적인 분위기는 부정적.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['투자주의', '급락', '단타']</t>
+          <t>['투자주의', '급락', '외인매수']</t>
         </is>
       </c>
       <c r="X21" t="n">

--- a/data/trending_integrated_20260914_15.xlsx
+++ b/data/trending_integrated_20260914_15.xlsx
@@ -578,13 +578,13 @@
         <v>-0.28</v>
       </c>
       <c r="E2" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F2" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G2" t="n">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="H2" t="n">
         <v>17.67</v>
@@ -610,7 +610,7 @@
         <v>17.95</v>
       </c>
       <c r="O2" t="n">
-        <v>271258034675</v>
+        <v>271769737425</v>
       </c>
       <c r="P2" t="n">
         <v>22450</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>차세대 광반도체 및 광통신 테마 기대감 속 3연상 및 텐버거 전망. 시세 끝 및 급락 조심론도 공존.</t>
+          <t>차세대 광반도체 및 광통신 관련주로 언급되며, 3연상 기대감 속 공급과 매집 소식이 있으나 시세 끝 및 급락 가능성 경고도 존재.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광반도체', '광통신', '텐버거']</t>
+          <t>['광반도체', '광통신', '공급']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6850</v>
+        <v>6900</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+24.32%</t>
+          <t>+25.23%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F3" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G3" t="n">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="H3" t="n">
         <v>1.67</v>
@@ -702,7 +702,7 @@
         <v>1.68</v>
       </c>
       <c r="O3" t="n">
-        <v>78121775125</v>
+        <v>78614255725</v>
       </c>
       <c r="P3" t="n">
         <v>10360</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9190</v>
+        <v>9270</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+16.18%</t>
+          <t>+17.19%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.55</v>
       </c>
       <c r="E4" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F4" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G4" t="n">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="H4" t="n">
         <v>1.25</v>
@@ -794,7 +794,7 @@
         <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>124075390505</v>
+        <v>124911665015</v>
       </c>
       <c r="P4" t="n">
         <v>25050</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2925</v>
+        <v>2940</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+13.15%</t>
+          <t>+13.73%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.04</v>
       </c>
       <c r="E5" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G5" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H5" t="n">
         <v>3.6</v>
@@ -886,7 +886,7 @@
         <v>3.64</v>
       </c>
       <c r="O5" t="n">
-        <v>40188474729</v>
+        <v>40392219669</v>
       </c>
       <c r="P5" t="n">
         <v>6180</v>
@@ -946,13 +946,13 @@
         <v>-0.45</v>
       </c>
       <c r="E6" t="n">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="F6" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G6" t="n">
-        <v>332</v>
+        <v>359</v>
       </c>
       <c r="H6" t="n">
         <v>0.59</v>
@@ -978,7 +978,7 @@
         <v>1.04</v>
       </c>
       <c r="O6" t="n">
-        <v>312620497997</v>
+        <v>314047043022</v>
       </c>
       <c r="P6" t="n">
         <v>8100</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>6G 시대 개막 및 광전자, 빛샘전자 등 관련주 동반 상승 기대감. 국책사업 선정 시 8000원 이상 가치 주장.</t>
+          <t>6G 시대 개막 및 국책사업 선정 기대감으로 8000원 이상, 나아가 만원 이상 상승 전망 언급. 광전자 주가 상승에 따른 기대감도 존재.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1038,13 +1038,13 @@
         <v>0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F7" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G7" t="n">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="H7" t="n">
         <v>0.83</v>
@@ -1070,7 +1070,7 @@
         <v>0.82</v>
       </c>
       <c r="O7" t="n">
-        <v>48632871925</v>
+        <v>49067279995</v>
       </c>
       <c r="P7" t="n">
         <v>12800</v>
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2805</v>
+        <v>17200</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+7.06%</t>
+          <t>+7.10%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-2.39</v>
+        <v>0.31</v>
       </c>
       <c r="E8" t="n">
-        <v>81</v>
+        <v>145</v>
       </c>
       <c r="F8" t="n">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="G8" t="n">
-        <v>233</v>
+        <v>259</v>
       </c>
       <c r="H8" t="n">
-        <v>1.44</v>
+        <v>2.7</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,47 +1147,47 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>2620</v>
+        <v>16060</v>
       </c>
       <c r="K8" t="n">
-        <v>2745</v>
+        <v>16780</v>
       </c>
       <c r="L8" t="n">
-        <v>3145</v>
+        <v>18610</v>
       </c>
       <c r="M8" t="n">
-        <v>2700</v>
+        <v>16230</v>
       </c>
       <c r="N8" t="n">
-        <v>3.83</v>
+        <v>2.39</v>
       </c>
       <c r="O8" t="n">
-        <v>105548938535</v>
+        <v>282263886605</v>
       </c>
       <c r="P8" t="n">
-        <v>4810</v>
+        <v>30550</v>
       </c>
       <c r="Q8" t="n">
-        <v>1400</v>
+        <v>6100</v>
       </c>
       <c r="R8" t="n">
-        <v>-306000</v>
+        <v>-295000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>양자 보안 관련주로 부각되며 강한 상승세 시현. 매출액 및 영업이익 증가 추세, 4800원 전고점 돌파 기대. 투경 조건 진입 시 매도 권고.</t>
+          <t>AI 개발 속도 조절론이 호재로 작용할 수 있다는 기대감과 프로그램 매도에 대한 우려 공존. 보안주로서의 가능성 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['양자 보안', '매출액', '전고점 돌파']</t>
+          <t>['AI', '보안주', '프로그램매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1195,43 +1195,43 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>203650</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17080</v>
+        <v>2795</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+6.35%</t>
+          <t>+6.68%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.31</v>
+        <v>-2.39</v>
       </c>
       <c r="E9" t="n">
-        <v>144</v>
+        <v>83</v>
       </c>
       <c r="F9" t="n">
-        <v>89</v>
+        <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="H9" t="n">
-        <v>2.7</v>
+        <v>1.44</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,47 +1239,47 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>16060</v>
+        <v>2620</v>
       </c>
       <c r="K9" t="n">
-        <v>16780</v>
+        <v>2745</v>
       </c>
       <c r="L9" t="n">
-        <v>18610</v>
+        <v>3145</v>
       </c>
       <c r="M9" t="n">
-        <v>16230</v>
+        <v>2700</v>
       </c>
       <c r="N9" t="n">
-        <v>2.39</v>
+        <v>3.83</v>
       </c>
       <c r="O9" t="n">
-        <v>280888385405</v>
+        <v>105836745275</v>
       </c>
       <c r="P9" t="n">
-        <v>30550</v>
+        <v>4810</v>
       </c>
       <c r="Q9" t="n">
-        <v>6100</v>
+        <v>1400</v>
       </c>
       <c r="R9" t="n">
-        <v>-295000</v>
+        <v>-306000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>AI 개발 속도 조절론이 호재로 작용할 수 있다는 기대감과 프로그램 매도에 대한 우려 공존. 보안주로서의 가능성 언급.</t>
+          <t>양자 보안 관련주로 부각되며 강한 상승세 시현. 매출액 및 영업이익 증가 추세, 4800원 전고점 돌파 기대. 투경 조건 진입 시 매도 권고.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['AI', '보안주', '프로그램매도']</t>
+          <t>['양자 보안', '매출액', '전고점 돌파']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1287,12 +1287,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
@@ -1314,13 +1314,13 @@
         <v>-0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F10" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G10" t="n">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="H10" t="n">
         <v>28.81</v>
@@ -1346,7 +1346,7 @@
         <v>28.89</v>
       </c>
       <c r="O10" t="n">
-        <v>93501584925</v>
+        <v>96876166525</v>
       </c>
       <c r="P10" t="n">
         <v>35350</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>대형 상선 수주 (1.6조 원) 및 쇄빙선+LNG선+해상데이터센터 등 사업 전망. 증권사 목표가 상향 및 숏커버 기대감.</t>
+          <t>대형 상선 수주 성공 및 작년 실적 돌파 소식과 증권사 목표가 상향 언급, 숏커버 및 조선업 호황 기대감.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['수주', 'LNG선', '목표주가']</t>
+          <t>['수주', '조선업', '목표주가']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1406,13 +1406,13 @@
         <v>-0.62</v>
       </c>
       <c r="E11" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F11" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G11" t="n">
-        <v>902</v>
+        <v>942</v>
       </c>
       <c r="H11" t="n">
         <v>1.88</v>
@@ -1438,7 +1438,7 @@
         <v>2.5</v>
       </c>
       <c r="O11" t="n">
-        <v>178371604515</v>
+        <v>179240222055</v>
       </c>
       <c r="P11" t="n">
         <v>31500</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>AIDC 광통신 기술 발전 뉴스와 함께 향후 주가 상승에 대한 기대감 표출.</t>
+          <t>GPU 확보 및 AIDC 광통신 기술 성장 관련 뉴스 언급, 타 종목 대비 상승 흐름이 더딘 점에 대한 아쉬움과 함께 대장주로서의 상승 가능성 제기.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신', 'AIDC', '기술력']</t>
+          <t>['광통신', 'GPU', 'AIDC']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1498,13 +1498,13 @@
         <v>-0.54</v>
       </c>
       <c r="E12" t="n">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="F12" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G12" t="n">
-        <v>2247</v>
+        <v>2329</v>
       </c>
       <c r="H12" t="n">
         <v>0.75</v>
@@ -1530,7 +1530,7 @@
         <v>1.29</v>
       </c>
       <c r="O12" t="n">
-        <v>51237566340</v>
+        <v>51575331840</v>
       </c>
       <c r="P12" t="n">
         <v>21500</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14630</v>
+        <v>14660</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-1.97</v>
       </c>
       <c r="E13" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F13" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G13" t="n">
-        <v>843</v>
+        <v>858</v>
       </c>
       <c r="H13" t="n">
         <v>1.17</v>
@@ -1622,7 +1622,7 @@
         <v>3.14</v>
       </c>
       <c r="O13" t="n">
-        <v>126670746400</v>
+        <v>127191235040</v>
       </c>
       <c r="P13" t="n">
         <v>36200</v>
@@ -1682,13 +1682,13 @@
         <v>-0.36</v>
       </c>
       <c r="E14" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F14" t="n">
         <v>42</v>
       </c>
       <c r="G14" t="n">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="H14" t="n">
         <v>2.08</v>
@@ -1714,7 +1714,7 @@
         <v>2.44</v>
       </c>
       <c r="O14" t="n">
-        <v>17927680609</v>
+        <v>18070635241</v>
       </c>
       <c r="P14" t="n">
         <v>4795</v>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>249500</v>
+        <v>249000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-3.85%</t>
+          <t>-4.05%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="G15" t="n">
-        <v>1709</v>
+        <v>1782</v>
       </c>
       <c r="H15" t="n">
         <v>46.64</v>
@@ -1806,7 +1806,7 @@
         <v>46.71</v>
       </c>
       <c r="O15" t="n">
-        <v>3850531393250</v>
+        <v>4149274621250</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>AI 속도 조절론, 정치적 이슈, 미 선물 하락 등 복합적 악재 속 외국인·기관 매도세. 희망적인 전망은 찾아보기 어려움.</t>
+          <t>AI 속도 조절론 언급에도 불구하고 정치적 이슈와 국장 자체에 대한 부정적 인식, 외인 기관 매도세 관찰.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['AI', '외국인', '기관']</t>
+          <t>['AI', '외인', '국장']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>86700</v>
+        <v>87000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-4.52%</t>
+          <t>-4.19%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.03</v>
       </c>
       <c r="E16" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F16" t="n">
         <v>150</v>
       </c>
       <c r="G16" t="n">
-        <v>955</v>
+        <v>966</v>
       </c>
       <c r="H16" t="n">
         <v>23.56</v>
@@ -1898,7 +1898,7 @@
         <v>23.59</v>
       </c>
       <c r="O16" t="n">
-        <v>248342447750</v>
+        <v>256617626750</v>
       </c>
       <c r="P16" t="n">
         <v>139200</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>정부 경제 정책에 대한 불만과 외국인·기관의 움직임에 대한 관망세. '희망 회로' 그만 굴리자는 자조적인 의견도 존재.</t>
+          <t>오후 반등 기대감 및 국제 유가 상승에 따른 원전주 상승 가능성 언급, 그러나 정부 정책 및 잡주 언급으로 부정적 시각도 존재.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['정부정책', '외국인', '기관']</t>
+          <t>['원전', '유가', '반등']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1958,13 +1958,13 @@
         <v>-0.1</v>
       </c>
       <c r="E17" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F17" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G17" t="n">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="H17" t="n">
         <v>10.55</v>
@@ -1990,7 +1990,7 @@
         <v>10.65</v>
       </c>
       <c r="O17" t="n">
-        <v>82259294840</v>
+        <v>83050441560</v>
       </c>
       <c r="P17" t="n">
         <v>40350</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>공매도 세력에 대한 반발과 '대차해지 운동' 동참 촉구. 주가 상승에 대한 기대보다는 공매도 세력과의 싸움에 집중하는 모습.</t>
+          <t>주가 지키기를 위한 '대차해지운동' 독려가 반복적으로 나타나며, 개미 뭉치를 통한 공매도 대응 주장.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['대차해지', '공매도', '개미뭉치']</t>
+          <t>['대차해지', '공매도', '주주']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2056,7 +2056,7 @@
         <v>42</v>
       </c>
       <c r="G18" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H18" t="n">
         <v>0.22</v>
@@ -2082,7 +2082,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>60732469095</v>
+        <v>60960622695</v>
       </c>
       <c r="P18" t="n">
         <v>20850</v>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1692000</v>
+        <v>1697000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-6.62%</t>
+          <t>-6.35%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="G19" t="n">
-        <v>1677</v>
+        <v>1699</v>
       </c>
       <c r="H19" t="n">
         <v>50.47</v>
@@ -2174,7 +2174,7 @@
         <v>50.55</v>
       </c>
       <c r="O19" t="n">
-        <v>5980615719500</v>
+        <v>6405430820500</v>
       </c>
       <c r="P19" t="n">
         <v>2987000</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>정치적 불만과 '망할 정권' 언급이 주를 이루며, 반도체 시장 및 주가 하락에 대한 부정적 전망만 가득.</t>
+          <t>정치적 요인 및 거시 경제 불안으로 인한 하락세 언급, 반도체 시세 끝 및 향후 전망에 대한 부정적 의견 지배적.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['반도체', '하락', '정치']</t>
+          <t>['반도체', '하락세', '경제']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13490</v>
+        <v>13600</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-8.29%</t>
+          <t>-7.55%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="F20" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G20" t="n">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2266,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>34286322880</v>
+        <v>34405866880</v>
       </c>
       <c r="P20" t="n">
         <v>19380</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10820</v>
+        <v>10770</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-13.09%</t>
+          <t>-13.49%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.51</v>
       </c>
       <c r="E21" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="F21" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G21" t="n">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="H21" t="n">
         <v>17.58</v>
@@ -2358,7 +2358,7 @@
         <v>17.07</v>
       </c>
       <c r="O21" t="n">
-        <v>70897379240</v>
+        <v>71130915920</v>
       </c>
       <c r="P21" t="n">
         <v>14350</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>투자주의 종목 지정 및 급락세 속 투자자들의 짜증과 불안감. 외인 대량 매수 언급도 있으나 전반적인 분위기는 부정적.</t>
+          <t>투자주의 종목 지정과 큰 폭의 하락세를 보이며, 외인 매수세 언급에도 불구하고 부정적인 시장 분위기 감지.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['투자주의', '급락', '외인매수']</t>
+          <t>['투자주의', '하락세', '외인']</t>
         </is>
       </c>
       <c r="X21" t="n">

--- a/data/trending_integrated_20260914_15.xlsx
+++ b/data/trending_integrated_20260914_15.xlsx
@@ -578,13 +578,13 @@
         <v>-0.28</v>
       </c>
       <c r="E2" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F2" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G2" t="n">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="H2" t="n">
         <v>17.67</v>
@@ -610,7 +610,7 @@
         <v>17.95</v>
       </c>
       <c r="O2" t="n">
-        <v>271769737425</v>
+        <v>271771637375</v>
       </c>
       <c r="P2" t="n">
         <v>22450</v>
@@ -626,12 +626,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>차세대 광반도체 및 광통신 관련주로 언급되며, 3연상 기대감 속 공급과 매집 소식이 있으나 시세 끝 및 급락 가능성 경고도 존재.</t>
+          <t>차세대 광반도체 및 광통신 관련주로 부각되며 공급과 모건스텐리 매집 소식이 있었으나, 시세 끝 조심 및 무너진다는 의견도 존재.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         <v>70</v>
       </c>
       <c r="G3" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H3" t="n">
         <v>1.67</v>
@@ -702,7 +702,7 @@
         <v>1.68</v>
       </c>
       <c r="O3" t="n">
-        <v>78614255725</v>
+        <v>78631015825</v>
       </c>
       <c r="P3" t="n">
         <v>10360</v>
@@ -762,13 +762,13 @@
         <v>0.55</v>
       </c>
       <c r="E4" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F4" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G4" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="H4" t="n">
         <v>1.25</v>
@@ -794,7 +794,7 @@
         <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>124911665015</v>
+        <v>124944369575</v>
       </c>
       <c r="P4" t="n">
         <v>25050</v>
@@ -854,13 +854,13 @@
         <v>-0.04</v>
       </c>
       <c r="E5" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F5" t="n">
         <v>51</v>
       </c>
       <c r="G5" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H5" t="n">
         <v>3.6</v>
@@ -886,7 +886,7 @@
         <v>3.64</v>
       </c>
       <c r="O5" t="n">
-        <v>40392219669</v>
+        <v>40396667889</v>
       </c>
       <c r="P5" t="n">
         <v>6180</v>
@@ -952,7 +952,7 @@
         <v>130</v>
       </c>
       <c r="G6" t="n">
-        <v>359</v>
+        <v>384</v>
       </c>
       <c r="H6" t="n">
         <v>0.59</v>
@@ -978,7 +978,7 @@
         <v>1.04</v>
       </c>
       <c r="O6" t="n">
-        <v>314047043022</v>
+        <v>314121260022</v>
       </c>
       <c r="P6" t="n">
         <v>8100</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>6G 시대 개막 및 국책사업 선정 기대감으로 8000원 이상, 나아가 만원 이상 상승 전망 언급. 광전자 주가 상승에 따른 기대감도 존재.</t>
+          <t>6G, 국책사업 선정 등 잠재적 호재 언급 및 광전자 관련주 상승에 따른 기대감, 거래량 증가 및 '대장주'로서의 가능성 제시.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['6G', '국책사업', '광전자']</t>
+          <t>['6G', '국책사업', '거래량']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1038,13 +1038,13 @@
         <v>0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F7" t="n">
         <v>43</v>
       </c>
       <c r="G7" t="n">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="H7" t="n">
         <v>0.83</v>
@@ -1070,7 +1070,7 @@
         <v>0.82</v>
       </c>
       <c r="O7" t="n">
-        <v>49067279995</v>
+        <v>49074491425</v>
       </c>
       <c r="P7" t="n">
         <v>12800</v>
@@ -1130,13 +1130,13 @@
         <v>0.31</v>
       </c>
       <c r="E8" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="F8" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G8" t="n">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="H8" t="n">
         <v>2.7</v>
@@ -1162,7 +1162,7 @@
         <v>2.39</v>
       </c>
       <c r="O8" t="n">
-        <v>282263886605</v>
+        <v>282304083005</v>
       </c>
       <c r="P8" t="n">
         <v>30550</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>AI 개발 속도 조절론이 호재로 작용할 수 있다는 기대감과 프로그램 매도에 대한 우려 공존. 보안주로서의 가능성 언급.</t>
+          <t>AI 개발 속도 조절론 속에서 보안주로서의 역할 기대, 프로그램 매도세 속에서도 상승 가능성 및 2연상 기대감 존재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['AI', '보안주', '프로그램매도']</t>
+          <t>['AI', '보안주', '속도조절론']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1222,13 +1222,13 @@
         <v>-2.39</v>
       </c>
       <c r="E9" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F9" t="n">
         <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="H9" t="n">
         <v>1.44</v>
@@ -1254,7 +1254,7 @@
         <v>3.83</v>
       </c>
       <c r="O9" t="n">
-        <v>105836745275</v>
+        <v>105846094550</v>
       </c>
       <c r="P9" t="n">
         <v>4810</v>
@@ -1314,13 +1314,13 @@
         <v>-0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F10" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G10" t="n">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="H10" t="n">
         <v>28.81</v>
@@ -1346,7 +1346,7 @@
         <v>28.89</v>
       </c>
       <c r="O10" t="n">
-        <v>96876166525</v>
+        <v>96876431725</v>
       </c>
       <c r="P10" t="n">
         <v>35350</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>대형 상선 수주 성공 및 작년 실적 돌파 소식과 증권사 목표가 상향 언급, 숏커버 및 조선업 호황 기대감.</t>
+          <t>쇄빙선, LNG선, 해상데이터센터 관련 수주 기대감과 함께 증권사 목표주가 상향, 대차거래 잔고 감소 등 긍정적 요인 분석.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['수주', '조선업', '목표주가']</t>
+          <t>['수주', '목표주가', '대차거래']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1409,10 +1409,10 @@
         <v>233</v>
       </c>
       <c r="F11" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G11" t="n">
-        <v>942</v>
+        <v>980</v>
       </c>
       <c r="H11" t="n">
         <v>1.88</v>
@@ -1438,7 +1438,7 @@
         <v>2.5</v>
       </c>
       <c r="O11" t="n">
-        <v>179240222055</v>
+        <v>179281054875</v>
       </c>
       <c r="P11" t="n">
         <v>31500</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>GPU 확보 및 AIDC 광통신 기술 성장 관련 뉴스 언급, 타 종목 대비 상승 흐름이 더딘 점에 대한 아쉬움과 함께 대장주로서의 상승 가능성 제기.</t>
+          <t>AIDC 광통신 기술 부각 및 GPU 확보 뉴스, 추석 전 25,000원 돌파 가능성 등 긍정적 전망 제시.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신', 'GPU', 'AIDC']</t>
+          <t>['광통신', 'AIDC', 'GPU']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1498,13 +1498,13 @@
         <v>-0.54</v>
       </c>
       <c r="E12" t="n">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="F12" t="n">
         <v>146</v>
       </c>
       <c r="G12" t="n">
-        <v>2329</v>
+        <v>2344</v>
       </c>
       <c r="H12" t="n">
         <v>0.75</v>
@@ -1530,7 +1530,7 @@
         <v>1.29</v>
       </c>
       <c r="O12" t="n">
-        <v>51575331840</v>
+        <v>51582412860</v>
       </c>
       <c r="P12" t="n">
         <v>21500</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>신약 개발 관련 심포지엄 및 임상 결과 발표 임박. 글로벌 제약사 협력 및 기대감.</t>
+          <t>회사의 자신감을 바탕으로 한 글로벌 발표 및 유튜브 방송 공개 예정. 임상 결과에 대한 긍정적 기대감.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['신약개발', '임상결과', '바이오']</t>
+          <t>['기획주', '임상결과', '바이오 신약']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1590,13 +1590,13 @@
         <v>-1.97</v>
       </c>
       <c r="E13" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F13" t="n">
         <v>170</v>
       </c>
       <c r="G13" t="n">
-        <v>858</v>
+        <v>884</v>
       </c>
       <c r="H13" t="n">
         <v>1.17</v>
@@ -1622,7 +1622,7 @@
         <v>3.14</v>
       </c>
       <c r="O13" t="n">
-        <v>127191235040</v>
+        <v>127225290220</v>
       </c>
       <c r="P13" t="n">
         <v>36200</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>이란-걸프 국가 회담 연기 및 호르무즈 해협 긴장 고조로 인한 유가 급등 기대감. 외인·기관 매도세 속 저가 매수 기회 논의.</t>
+          <t>호르무즈 해협 회담 연기 및 국제유가 폭등 가능성 언급, 유가 상승에 따른 수혜 기대감 존재하나 외인/기관 매도세 주의.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['국제유가', '호르무즈', '회담연기']</t>
+          <t>['유가', '호르무즈', '회담연기']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1682,13 +1682,13 @@
         <v>-0.36</v>
       </c>
       <c r="E14" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F14" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G14" t="n">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="H14" t="n">
         <v>2.08</v>
@@ -1714,7 +1714,7 @@
         <v>2.44</v>
       </c>
       <c r="O14" t="n">
-        <v>18070635241</v>
+        <v>18077632237</v>
       </c>
       <c r="P14" t="n">
         <v>4795</v>
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="G15" t="n">
-        <v>1782</v>
+        <v>1823</v>
       </c>
       <c r="H15" t="n">
         <v>46.64</v>
@@ -1806,7 +1806,7 @@
         <v>46.71</v>
       </c>
       <c r="O15" t="n">
-        <v>4149274621250</v>
+        <v>4149741745250</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>AI 속도 조절론 언급에도 불구하고 정치적 이슈와 국장 자체에 대한 부정적 인식, 외인 기관 매도세 관찰.</t>
+          <t>AI 속도 조절론, 정치적 이슈, 악재에 대한 과도한 반응, 외인/기관 매도세 등이 언급되며 부정적인 전망 제시.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['AI', '외인', '국장']</t>
+          <t>['AI', '악재', '외인매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1866,13 +1866,13 @@
         <v>-0.03</v>
       </c>
       <c r="E16" t="n">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="F16" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G16" t="n">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="H16" t="n">
         <v>23.56</v>
@@ -1898,7 +1898,7 @@
         <v>23.59</v>
       </c>
       <c r="O16" t="n">
-        <v>256617626750</v>
+        <v>256657211750</v>
       </c>
       <c r="P16" t="n">
         <v>139200</v>
@@ -1958,13 +1958,13 @@
         <v>-0.1</v>
       </c>
       <c r="E17" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F17" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G17" t="n">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="H17" t="n">
         <v>10.55</v>
@@ -1990,7 +1990,7 @@
         <v>10.65</v>
       </c>
       <c r="O17" t="n">
-        <v>83050441560</v>
+        <v>83100211840</v>
       </c>
       <c r="P17" t="n">
         <v>40350</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주가 지키기를 위한 '대차해지운동' 독려가 반복적으로 나타나며, 개미 뭉치를 통한 공매도 대응 주장.</t>
+          <t>공매도 세력에 대한 비판과 함께 '대차해지운동' 독려, 주주들의 적극적인 참여 요구.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['대차해지', '공매도', '주주']</t>
+          <t>['대차해지', '공매도', '주주운동']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2050,7 +2050,7 @@
         <v>-0.72</v>
       </c>
       <c r="E18" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F18" t="n">
         <v>42</v>
@@ -2082,7 +2082,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>60960622695</v>
+        <v>60966382695</v>
       </c>
       <c r="P18" t="n">
         <v>20850</v>
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="G19" t="n">
-        <v>1699</v>
+        <v>1734</v>
       </c>
       <c r="H19" t="n">
         <v>50.47</v>
@@ -2174,7 +2174,7 @@
         <v>50.55</v>
       </c>
       <c r="O19" t="n">
-        <v>6405430820500</v>
+        <v>6405525852500</v>
       </c>
       <c r="P19" t="n">
         <v>2987000</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>정치적 요인 및 거시 경제 불안으로 인한 하락세 언급, 반도체 시세 끝 및 향후 전망에 대한 부정적 의견 지배적.</t>
+          <t>국가 정책 및 정치적 이슈, 반도체 시장 약세 전망, 주가 하락에 대한 불안감과 투매 심리 확산.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['반도체', '하락세', '경제']</t>
+          <t>['반도체', '주가하락', '시장전망']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2234,13 +2234,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F20" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G20" t="n">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2266,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>34405866880</v>
+        <v>34418528480</v>
       </c>
       <c r="P20" t="n">
         <v>19380</v>
@@ -2329,10 +2329,10 @@
         <v>137</v>
       </c>
       <c r="F21" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G21" t="n">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="H21" t="n">
         <v>17.58</v>
@@ -2358,7 +2358,7 @@
         <v>17.07</v>
       </c>
       <c r="O21" t="n">
-        <v>71130915920</v>
+        <v>71187555350</v>
       </c>
       <c r="P21" t="n">
         <v>14350</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>투자주의 종목 지정과 큰 폭의 하락세를 보이며, 외인 매수세 언급에도 불구하고 부정적인 시장 분위기 감지.</t>
+          <t>급격한 하락세와 투자 주의 종목 지정, 외인 대량 매수에도 불구하고 불안정한 흐름과 하한가 우려 제기.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['투자주의', '하락세', '외인']</t>
+          <t>['하락', '투자주의', '외인매수']</t>
         </is>
       </c>
       <c r="X21" t="n">
